--- a/tests/fixtures/sheetjs-report.xlsx
+++ b/tests/fixtures/sheetjs-report.xlsx
@@ -427,7 +427,7 @@
         <v>1200.5</v>
       </c>
       <c r="C3" s="2" t="d">
-        <v>2024-02-28T18:00:00.000Z</v>
+        <v>2024-02-29T00:00:00.000Z</v>
       </c>
     </row>
     <row r="5">
